--- a/data/trans_dic/P57_AC_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P57_AC_R-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo confidencial bajo (Duke)</t>
+          <t>Población con apoyo confidencial bajo (Duke) (tasa de respuesta: 99,29%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>75,41; 84,84</t>
+          <t>75,16; 84,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>67,6; 78,56</t>
+          <t>67,26; 78,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>77,1; 86,59</t>
+          <t>76,69; 86,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45,11; 59,53</t>
+          <t>44,84; 59,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>85,45; 93,23</t>
+          <t>85,74; 93,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,5; 86,19</t>
+          <t>75,93; 86,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,95; 87,37</t>
+          <t>78,02; 87,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>54,75; 64,28</t>
+          <t>54,0; 63,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>81,6; 87,75</t>
+          <t>81,93; 87,79</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>73,38; 80,81</t>
+          <t>73,55; 80,73</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>78,99; 85,67</t>
+          <t>78,91; 85,76</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>51,21; 59,83</t>
+          <t>51,2; 60,04</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>54,23; 63,3</t>
+          <t>54,2; 63,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>50,69; 59,58</t>
+          <t>50,44; 59,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>76,09; 83,21</t>
+          <t>76,06; 83,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>58,23; 68,96</t>
+          <t>57,2; 68,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>61,84; 70,16</t>
+          <t>61,83; 69,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,46; 61,82</t>
+          <t>52,49; 61,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>77,08; 84,04</t>
+          <t>77,06; 83,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>53,2; 61,37</t>
+          <t>53,45; 61,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>59,45; 65,75</t>
+          <t>59,12; 65,44</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53,02; 59,47</t>
+          <t>52,81; 59,53</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>77,62; 82,6</t>
+          <t>77,86; 82,78</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>56,79; 63,72</t>
+          <t>56,57; 63,61</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>56,06; 67,1</t>
+          <t>56,55; 67,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>58,73; 69,76</t>
+          <t>59,28; 69,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66,15; 75,83</t>
+          <t>66,27; 75,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>38,99; 51,05</t>
+          <t>39,62; 50,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>52,12; 63,08</t>
+          <t>51,53; 62,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>68,5; 78,2</t>
+          <t>68,36; 77,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>75,86; 84,82</t>
+          <t>75,97; 84,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>46,14; 55,46</t>
+          <t>46,01; 55,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>55,14; 63,23</t>
+          <t>55,54; 62,99</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>65,02; 72,52</t>
+          <t>65,44; 72,85</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>72,6; 79,18</t>
+          <t>72,59; 79,36</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>44,46; 51,85</t>
+          <t>44,52; 51,14</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>66,04; 76,15</t>
+          <t>66,21; 75,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>46,36; 57,23</t>
+          <t>46,71; 57,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41,05; 51,45</t>
+          <t>40,66; 51,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25,58; 39,29</t>
+          <t>26,27; 39,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>65,22; 74,04</t>
+          <t>64,88; 74,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,02; 66,58</t>
+          <t>55,85; 66,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,12; 59,32</t>
+          <t>49,69; 60,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,23; 36,61</t>
+          <t>17,31; 36,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>67,01; 73,62</t>
+          <t>67,21; 73,64</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52,97; 60,15</t>
+          <t>52,73; 60,14</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46,77; 54,49</t>
+          <t>46,64; 54,13</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21,55; 35,53</t>
+          <t>22,82; 35,36</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>72,6; 84,83</t>
+          <t>73,06; 84,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>46,23; 60,37</t>
+          <t>45,79; 60,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>81,46; 90,87</t>
+          <t>81,13; 90,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>87,64; 95,21</t>
+          <t>87,44; 95,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>80,66; 90,26</t>
+          <t>81,03; 90,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>65,78; 77,81</t>
+          <t>65,09; 77,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>82,49; 90,92</t>
+          <t>82,43; 91,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>88,91; 94,76</t>
+          <t>89,08; 94,72</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>78,52; 86,31</t>
+          <t>78,8; 86,12</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>57,8; 67,2</t>
+          <t>57,71; 67,73</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>83,28; 90,05</t>
+          <t>83,52; 89,78</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>89,43; 94,42</t>
+          <t>89,33; 94,31</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>63,84; 75,08</t>
+          <t>63,66; 74,98</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>55,15; 67,03</t>
+          <t>55,12; 67,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>71,77; 82,4</t>
+          <t>71,91; 82,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>33,33; 43,66</t>
+          <t>33,93; 43,87</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>68,22; 78,65</t>
+          <t>68,53; 78,76</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>71,01; 81,3</t>
+          <t>70,93; 80,99</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>71,55; 81,87</t>
+          <t>71,8; 81,97</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>35,24; 44,1</t>
+          <t>35,21; 44,84</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>67,58; 75,49</t>
+          <t>67,75; 75,68</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>65,14; 72,99</t>
+          <t>64,86; 72,66</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>73,01; 80,32</t>
+          <t>73,0; 80,46</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>35,77; 42,86</t>
+          <t>35,6; 42,38</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>48,03; 56,1</t>
+          <t>48,05; 56,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>55,76; 64,2</t>
+          <t>55,93; 64,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>79,04; 84,88</t>
+          <t>78,62; 85,23</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>56,46; 65,94</t>
+          <t>56,41; 66,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>45,04; 52,74</t>
+          <t>45,03; 53,09</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,62; 72,84</t>
+          <t>65,45; 72,87</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,61; 88,03</t>
+          <t>82,63; 88,08</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>59,3; 66,52</t>
+          <t>58,92; 66,68</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>47,84; 53,51</t>
+          <t>47,68; 53,64</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>61,78; 67,25</t>
+          <t>62,2; 67,68</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>81,65; 86,07</t>
+          <t>81,69; 85,8</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>59,11; 65,06</t>
+          <t>58,98; 65,14</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>77,07; 82,81</t>
+          <t>76,63; 83,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>86,93; 91,53</t>
+          <t>86,72; 91,53</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>90,06; 93,9</t>
+          <t>89,92; 93,99</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27,57; 85,41</t>
+          <t>28,2; 85,75</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>83,84; 88,49</t>
+          <t>83,65; 88,58</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>85,97; 90,79</t>
+          <t>86,22; 90,8</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>91,62; 95,13</t>
+          <t>91,54; 95,15</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>84,94; 89,32</t>
+          <t>84,91; 89,39</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>81,31; 85,03</t>
+          <t>81,34; 85,17</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>87,29; 90,56</t>
+          <t>87,28; 90,44</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>91,38; 94,03</t>
+          <t>91,48; 94,09</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>45,48; 86,5</t>
+          <t>44,93; 86,71</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>66,31; 69,51</t>
+          <t>66,37; 69,67</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>64,6; 68,03</t>
+          <t>64,68; 67,97</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>77,55; 80,41</t>
+          <t>77,61; 80,47</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>42,97; 61,91</t>
+          <t>43,84; 61,72</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>69,09; 72,13</t>
+          <t>69,12; 72,37</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>71,68; 74,62</t>
+          <t>71,8; 74,75</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>80,87; 83,32</t>
+          <t>80,77; 83,42</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>56,56; 63,26</t>
+          <t>56,74; 63,16</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>68,26; 70,49</t>
+          <t>68,26; 70,39</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>68,72; 70,99</t>
+          <t>68,67; 70,9</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>79,66; 81,6</t>
+          <t>79,7; 81,55</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>50,74; 61,7</t>
+          <t>51,79; 61,75</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo confidencial bajo (Duke)</t>
+          <t>Población con apoyo confidencial bajo (Duke) (tasa de respuesta: 99,29%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>205872; 231629</t>
+          <t>205208; 231554</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>196189; 227996</t>
+          <t>195191; 227032</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>221130; 248363</t>
+          <t>219976; 246912</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>140156; 184967</t>
+          <t>139318; 184430</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>222885; 243187</t>
+          <t>223655; 243473</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>216698; 244119</t>
+          <t>215081; 243801</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>222777; 249686</t>
+          <t>222983; 250766</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>157247; 184606</t>
+          <t>155092; 182994</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>435617; 468472</t>
+          <t>437373; 468676</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>420817; 463389</t>
+          <t>421786; 462964</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>452331; 490572</t>
+          <t>451851; 491085</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>306190; 357712</t>
+          <t>306149; 358970</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>266787; 311445</t>
+          <t>266657; 310743</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>255238; 300018</t>
+          <t>254014; 301529</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>379327; 414797</t>
+          <t>379187; 415381</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>299285; 354398</t>
+          <t>293993; 353412</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>311631; 353561</t>
+          <t>311580; 352304</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>274123; 323075</t>
+          <t>274284; 320959</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>399756; 435842</t>
+          <t>399645; 435032</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>272976; 314875</t>
+          <t>274217; 313314</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>592135; 654849</t>
+          <t>588812; 651702</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>544103; 610220</t>
+          <t>541944; 610825</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>789484; 840181</t>
+          <t>791989; 842035</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>583251; 654376</t>
+          <t>580976; 653247</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>178743; 213932</t>
+          <t>180313; 215669</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>189704; 225354</t>
+          <t>191477; 224604</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>210172; 240927</t>
+          <t>210532; 241305</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>119618; 156605</t>
+          <t>121539; 154293</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>174814; 211575</t>
+          <t>172824; 209917</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>232909; 265896</t>
+          <t>232448; 264928</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>253182; 283081</t>
+          <t>253550; 283022</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>151562; 182159</t>
+          <t>151130; 181618</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>360776; 413709</t>
+          <t>363402; 412139</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>431092; 480817</t>
+          <t>433905; 483062</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>472967; 515804</t>
+          <t>472856; 516972</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>282443; 329357</t>
+          <t>282785; 324860</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>236877; 273144</t>
+          <t>237490; 271651</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>171868; 212153</t>
+          <t>173150; 212990</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>151039; 189323</t>
+          <t>149593; 188094</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>78882; 121167</t>
+          <t>81025; 121919</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>242248; 275009</t>
+          <t>240983; 275361</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>216779; 257633</t>
+          <t>216114; 256247</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>189209; 228525</t>
+          <t>191435; 231490</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>80228; 170482</t>
+          <t>80601; 170080</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>489272; 537486</t>
+          <t>490752; 537645</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>401366; 455708</t>
+          <t>399557; 455690</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>352279; 410434</t>
+          <t>351291; 407656</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>166823; 275033</t>
+          <t>176614; 273690</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>147596; 172457</t>
+          <t>148533; 172632</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>97829; 127734</t>
+          <t>96901; 128028</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>172069; 191944</t>
+          <t>171354; 190766</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>156046; 169538</t>
+          <t>155691; 170231</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>167514; 187450</t>
+          <t>168274; 187300</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>143852; 170172</t>
+          <t>142345; 169491</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>180312; 198729</t>
+          <t>180184; 199773</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>185170; 197359</t>
+          <t>185531; 197280</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>322693; 354729</t>
+          <t>323851; 353951</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>248703; 289145</t>
+          <t>248328; 291441</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>357941; 387044</t>
+          <t>358985; 385884</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>345492; 364766</t>
+          <t>345129; 364362</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>172889; 203312</t>
+          <t>172386; 203061</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>148803; 180859</t>
+          <t>148724; 183469</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>188849; 216805</t>
+          <t>189203; 216090</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>89725; 117512</t>
+          <t>91322; 118096</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>189759; 218754</t>
+          <t>190600; 219080</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>198061; 226765</t>
+          <t>197852; 225907</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>194019; 222022</t>
+          <t>194692; 222283</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>90460; 113192</t>
+          <t>90361; 115085</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>370998; 414382</t>
+          <t>371935; 415430</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>357483; 400551</t>
+          <t>355906; 398759</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>390104; 429146</t>
+          <t>390022; 429917</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>188072; 225378</t>
+          <t>187213; 222822</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>295405; 345054</t>
+          <t>295509; 347277</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>365151; 420416</t>
+          <t>366260; 420229</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>516165; 554328</t>
+          <t>513407; 556576</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>347429; 405750</t>
+          <t>347120; 406737</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>287014; 336087</t>
+          <t>286980; 338320</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>450138; 499661</t>
+          <t>448979; 499914</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>565361; 602445</t>
+          <t>565498; 602826</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>374730; 420382</t>
+          <t>372366; 421367</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>599122; 670030</t>
+          <t>597082; 671678</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>828409; 901731</t>
+          <t>834048; 907471</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1092031; 1151083</t>
+          <t>1092526; 1147481</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>737221; 811490</t>
+          <t>735601; 812529</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>572051; 614624</t>
+          <t>568802; 616320</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>673848; 709543</t>
+          <t>672207; 709547</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>701195; 731064</t>
+          <t>700091; 731802</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>255337; 790986</t>
+          <t>261141; 794057</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>655922; 692307</t>
+          <t>654439; 693046</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>706440; 746118</t>
+          <t>708505; 746200</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>755022; 784003</t>
+          <t>754396; 784110</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>608732; 640088</t>
+          <t>608526; 640598</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1239585; 1296377</t>
+          <t>1240130; 1298518</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1393984; 1446204</t>
+          <t>1393845; 1444292</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1464476; 1506955</t>
+          <t>1466082; 1507931</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>747166; 1420939</t>
+          <t>738102; 1424370</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2170969; 2275537</t>
+          <t>2172811; 2281084</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2195742; 2312300</t>
+          <t>2198487; 2310203</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2618813; 2715505</t>
+          <t>2620694; 2717371</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1473323; 2122379</t>
+          <t>1502962; 2115993</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2333250; 2435811</t>
+          <t>2334164; 2444053</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2536064; 2640140</t>
+          <t>2540611; 2644727</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2847958; 2934358</t>
+          <t>2844493; 2937690</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1927645; 2155887</t>
+          <t>1933782; 2152435</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>4539778; 4688116</t>
+          <t>4540249; 4681898</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4767294; 4924822</t>
+          <t>4763531; 4918237</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5495187; 5628988</t>
+          <t>5497943; 5625830</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>3468951; 4218069</t>
+          <t>3540564; 4221190</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P57_AC_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P57_AC_R-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>54,71%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>57,37%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>75,16; 84,82</t>
+          <t>75,22; 84,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>67,26; 78,23</t>
+          <t>67,02; 78,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76,69; 86,09</t>
+          <t>76,88; 86,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44,84; 59,36</t>
+          <t>48,83; 60,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>85,74; 93,34</t>
+          <t>85,72; 93,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,93; 86,07</t>
+          <t>76,58; 86,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,02; 87,74</t>
+          <t>78,8; 87,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>54,0; 63,72</t>
+          <t>55,48; 64,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>81,93; 87,79</t>
+          <t>81,75; 87,96</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>73,55; 80,73</t>
+          <t>73,52; 80,61</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>78,91; 85,76</t>
+          <t>79,53; 85,88</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>51,2; 60,04</t>
+          <t>53,69; 61,3</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>57,6%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>60,4%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>54,2; 63,16</t>
+          <t>53,96; 62,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>50,44; 59,88</t>
+          <t>50,71; 59,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>76,06; 83,33</t>
+          <t>76,07; 83,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>57,2; 68,77</t>
+          <t>57,79; 68,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>61,83; 69,91</t>
+          <t>62,39; 70,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,49; 61,42</t>
+          <t>52,62; 61,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>77,06; 83,88</t>
+          <t>77,03; 84,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>53,45; 61,07</t>
+          <t>53,42; 61,28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>59,12; 65,44</t>
+          <t>59,64; 65,64</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>52,81; 59,53</t>
+          <t>52,96; 59,48</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>77,86; 82,78</t>
+          <t>77,56; 82,81</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>56,57; 63,61</t>
+          <t>57,15; 63,8</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>48,94%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>56,55; 67,64</t>
+          <t>56,2; 67,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>59,28; 69,53</t>
+          <t>59,05; 69,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66,27; 75,95</t>
+          <t>66,02; 76,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>39,62; 50,29</t>
+          <t>40,89; 51,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>51,53; 62,58</t>
+          <t>51,52; 62,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>68,36; 77,91</t>
+          <t>68,1; 78,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>75,97; 84,8</t>
+          <t>76,62; 85,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>46,01; 55,29</t>
+          <t>47,45; 57,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>55,54; 62,99</t>
+          <t>55,67; 63,17</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>65,44; 72,85</t>
+          <t>65,51; 72,52</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>72,59; 79,36</t>
+          <t>72,76; 79,38</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>44,52; 51,14</t>
+          <t>45,46; 52,74</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>35,0%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>66,21; 75,74</t>
+          <t>66,31; 75,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>46,71; 57,46</t>
+          <t>46,71; 57,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40,66; 51,12</t>
+          <t>40,52; 51,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,27; 39,53</t>
+          <t>27,65; 40,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>64,88; 74,13</t>
+          <t>64,17; 73,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,85; 66,22</t>
+          <t>56,46; 66,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,69; 60,09</t>
+          <t>49,22; 60,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,31; 36,53</t>
+          <t>32,24; 41,14</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>67,21; 73,64</t>
+          <t>66,78; 73,03</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52,73; 60,14</t>
+          <t>52,82; 60,43</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46,64; 54,13</t>
+          <t>46,54; 54,45</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22,82; 35,36</t>
+          <t>31,08; 38,93</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,31%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>73,06; 84,91</t>
+          <t>73,42; 84,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>45,79; 60,5</t>
+          <t>46,63; 60,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>81,13; 90,32</t>
+          <t>81,31; 90,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>87,44; 95,6</t>
+          <t>87,28; 95,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>81,03; 90,19</t>
+          <t>80,47; 90,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>65,09; 77,5</t>
+          <t>64,9; 77,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>82,43; 91,39</t>
+          <t>82,65; 91,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>89,08; 94,72</t>
+          <t>89,32; 95,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>78,8; 86,12</t>
+          <t>78,65; 86,12</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>57,71; 67,73</t>
+          <t>57,84; 67,31</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>83,52; 89,78</t>
+          <t>83,28; 89,61</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>89,33; 94,31</t>
+          <t>89,67; 94,49</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>40,73%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>63,66; 74,98</t>
+          <t>63,14; 74,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>55,12; 67,99</t>
+          <t>55,43; 67,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>71,91; 82,12</t>
+          <t>71,85; 82,11</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>33,93; 43,87</t>
+          <t>35,63; 45,68</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>68,53; 78,76</t>
+          <t>68,1; 78,62</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>70,93; 80,99</t>
+          <t>70,18; 81,06</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>71,8; 81,97</t>
+          <t>71,21; 81,6</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>35,21; 44,84</t>
+          <t>36,16; 45,36</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>67,75; 75,68</t>
+          <t>67,94; 75,48</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>64,86; 72,66</t>
+          <t>64,75; 72,88</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>73,0; 80,46</t>
+          <t>73,04; 80,43</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>35,6; 42,38</t>
+          <t>37,35; 44,43</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>63,29%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>48,05; 56,47</t>
+          <t>48,03; 56,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>55,93; 64,17</t>
+          <t>55,83; 64,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>78,62; 85,23</t>
+          <t>78,58; 84,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>56,41; 66,1</t>
+          <t>58,22; 66,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>45,03; 53,09</t>
+          <t>45,03; 53,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,45; 72,87</t>
+          <t>65,75; 72,69</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,63; 88,08</t>
+          <t>82,67; 88,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>58,92; 66,68</t>
+          <t>60,43; 66,98</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>47,68; 53,64</t>
+          <t>47,78; 53,65</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>62,2; 67,68</t>
+          <t>62,1; 67,52</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>81,69; 85,8</t>
+          <t>81,78; 85,84</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>58,98; 65,14</t>
+          <t>60,73; 66,1</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>85,96%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>76,63; 83,03</t>
+          <t>76,97; 82,78</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>86,72; 91,53</t>
+          <t>86,9; 91,33</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>89,92; 93,99</t>
+          <t>90,32; 93,93</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28,2; 85,75</t>
+          <t>81,63; 87,35</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>83,65; 88,58</t>
+          <t>83,69; 88,34</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>86,22; 90,8</t>
+          <t>85,98; 90,64</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>91,54; 95,15</t>
+          <t>91,28; 94,88</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>84,91; 89,39</t>
+          <t>84,87; 89,46</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>81,34; 85,17</t>
+          <t>81,26; 85,01</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>87,28; 90,44</t>
+          <t>87,3; 90,49</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>91,48; 94,09</t>
+          <t>91,54; 94,17</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>44,93; 86,71</t>
+          <t>83,99; 87,52</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>63,18%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>66,37; 69,67</t>
+          <t>66,57; 69,65</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>64,68; 67,97</t>
+          <t>64,64; 67,99</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>77,61; 80,47</t>
+          <t>77,74; 80,49</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>43,84; 61,72</t>
+          <t>60,61; 64,18</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>69,12; 72,37</t>
+          <t>69,18; 72,21</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>71,8; 74,75</t>
+          <t>71,74; 74,77</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>80,77; 83,42</t>
+          <t>80,88; 83,49</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>56,74; 63,16</t>
+          <t>62,44; 65,48</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>68,26; 70,39</t>
+          <t>68,15; 70,43</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>68,67; 70,9</t>
+          <t>68,75; 70,93</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>79,7; 81,55</t>
+          <t>79,62; 81,57</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>51,79; 61,75</t>
+          <t>62,04; 64,4</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>163338</t>
+          <t>174034</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>169638</t>
+          <t>187825</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>332977</t>
+          <t>361859</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>205208; 231554</t>
+          <t>205363; 229362</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>195191; 227032</t>
+          <t>194490; 227892</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>219976; 246912</t>
+          <t>220504; 248398</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>139318; 184430</t>
+          <t>155322; 191935</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>223655; 243473</t>
+          <t>223581; 242671</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>215081; 243801</t>
+          <t>216924; 244568</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>222983; 250766</t>
+          <t>225200; 251046</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>155092; 182994</t>
+          <t>173480; 200682</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>437373; 468676</t>
+          <t>436413; 469569</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>421786; 462964</t>
+          <t>421590; 462262</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>451851; 491085</t>
+          <t>455402; 491747</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>306149; 358970</t>
+          <t>338674; 386688</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>325402</t>
+          <t>332329</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>293936</t>
+          <t>313655</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>619338</t>
+          <t>645984</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>266657; 310743</t>
+          <t>265500; 309561</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>254014; 301529</t>
+          <t>255340; 301799</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>379187; 415381</t>
+          <t>379205; 414559</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>293993; 353412</t>
+          <t>303386; 357722</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>311580; 352304</t>
+          <t>314437; 353871</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>274284; 320959</t>
+          <t>274991; 322750</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>399645; 435032</t>
+          <t>399519; 436160</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>274217; 313314</t>
+          <t>290910; 333724</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>588812; 651702</t>
+          <t>593946; 653690</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>541944; 610825</t>
+          <t>543409; 610339</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>791989; 842035</t>
+          <t>788868; 842304</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>580976; 653247</t>
+          <t>611231; 682333</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>138011</t>
+          <t>140615</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>166443</t>
+          <t>174779</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>304454</t>
+          <t>315394</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>180313; 215669</t>
+          <t>179188; 214658</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>191477; 224604</t>
+          <t>190733; 225924</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>210532; 241305</t>
+          <t>209758; 241874</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>121539; 154293</t>
+          <t>125559; 156876</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>172824; 209917</t>
+          <t>172801; 208643</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>232448; 264928</t>
+          <t>231559; 266224</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>253550; 283022</t>
+          <t>255718; 284553</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>151130; 181618</t>
+          <t>160105; 192622</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>363402; 412139</t>
+          <t>364238; 413320</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>433905; 483062</t>
+          <t>434384; 480850</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>472856; 516972</t>
+          <t>474012; 517120</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>282785; 324860</t>
+          <t>292994; 339943</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>99386</t>
+          <t>121529</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>133284</t>
+          <t>150812</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>232670</t>
+          <t>272340</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>237490; 271651</t>
+          <t>237845; 271568</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>173150; 212990</t>
+          <t>173147; 211754</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>149593; 188094</t>
+          <t>149096; 190437</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>81025; 121919</t>
+          <t>101469; 147004</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>240983; 275361</t>
+          <t>238363; 274547</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>216114; 256247</t>
+          <t>218478; 256032</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>191435; 231490</t>
+          <t>189621; 231688</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>80601; 170080</t>
+          <t>132594; 169208</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>490752; 537645</t>
+          <t>487600; 533206</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>399557; 455690</t>
+          <t>400223; 457888</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>351291; 407656</t>
+          <t>350526; 410101</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>176614; 273690</t>
+          <t>241895; 302926</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>164606</t>
+          <t>188074</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>192391</t>
+          <t>210496</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>356997</t>
+          <t>398570</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>148533; 172632</t>
+          <t>149272; 172567</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>96901; 128028</t>
+          <t>98679; 127088</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>171354; 190766</t>
+          <t>171743; 190971</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>155691; 170231</t>
+          <t>178853; 194723</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>168274; 187300</t>
+          <t>167119; 188053</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>142345; 169491</t>
+          <t>141937; 168527</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>180184; 199773</t>
+          <t>180660; 199726</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>185531; 197280</t>
+          <t>202594; 216000</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>323851; 353951</t>
+          <t>323239; 353919</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>248328; 291441</t>
+          <t>248878; 289632</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>358985; 385884</t>
+          <t>357948; 385130</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>345129; 364362</t>
+          <t>387144; 407954</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>104155</t>
+          <t>109934</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>101569</t>
+          <t>107371</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>205724</t>
+          <t>217305</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>172386; 203061</t>
+          <t>171002; 202257</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>148724; 183469</t>
+          <t>149579; 181264</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>189203; 216090</t>
+          <t>189063; 216040</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>91322; 118096</t>
+          <t>96294; 123450</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>190600; 219080</t>
+          <t>189424; 218680</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>197852; 225907</t>
+          <t>195757; 226092</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>194692; 222283</t>
+          <t>193102; 221286</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>90361; 115085</t>
+          <t>95228; 119463</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>371935; 415430</t>
+          <t>372982; 414357</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>355906; 398759</t>
+          <t>355331; 399964</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>390022; 429917</t>
+          <t>390277; 429757</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>187213; 222822</t>
+          <t>199306; 237049</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>377145</t>
+          <t>444261</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>398226</t>
+          <t>483524</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>775371</t>
+          <t>927784</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>295509; 347277</t>
+          <t>295391; 344860</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>366260; 420229</t>
+          <t>365642; 421101</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>513407; 556576</t>
+          <t>513172; 554938</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>347120; 406737</t>
+          <t>412812; 473324</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>286980; 338320</t>
+          <t>286927; 337909</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>448979; 499914</t>
+          <t>451083; 498684</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>565498; 602826</t>
+          <t>565785; 602603</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>372366; 421367</t>
+          <t>457377; 506923</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>597082; 671678</t>
+          <t>598299; 671882</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>834048; 907471</t>
+          <t>832687; 905385</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1092526; 1147481</t>
+          <t>1093787; 1148059</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>735601; 812529</t>
+          <t>890284; 968892</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>576572</t>
+          <t>672871</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>625741</t>
+          <t>723471</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1202314</t>
+          <t>1396343</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>568802; 616320</t>
+          <t>571335; 614403</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>672207; 709547</t>
+          <t>673655; 707991</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>700091; 731802</t>
+          <t>703223; 731358</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>261141; 794057</t>
+          <t>649015; 694508</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>654439; 693046</t>
+          <t>654738; 691161</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>708505; 746200</t>
+          <t>706554; 744839</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>754396; 784110</t>
+          <t>752222; 781935</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>608526; 640598</t>
+          <t>703871; 741960</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1240130; 1298518</t>
+          <t>1238884; 1296021</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1393845; 1444292</t>
+          <t>1394105; 1445050</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1466082; 1507931</t>
+          <t>1467134; 1509188</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>738102; 1424370</t>
+          <t>1364416; 1421779</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1948615</t>
+          <t>2183645</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2081228</t>
+          <t>2351934</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>4029843</t>
+          <t>4535579</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2172811; 2281084</t>
+          <t>2179290; 2280419</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2198487; 2310203</t>
+          <t>2197132; 2310843</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2620694; 2717371</t>
+          <t>2625373; 2718147</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1502962; 2115993</t>
+          <t>2119131; 2243836</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2334164; 2444053</t>
+          <t>2336294; 2438619</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2540611; 2644727</t>
+          <t>2538399; 2645490</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2844493; 2937690</t>
+          <t>2848419; 2940170</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1933782; 2152435</t>
+          <t>2299379; 2411260</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>4540249; 4681898</t>
+          <t>4532346; 4684354</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4763531; 4918237</t>
+          <t>4769576; 4920842</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5497943; 5625830</t>
+          <t>5492814; 5627169</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>3540564; 4221190</t>
+          <t>4453342; 4622930</t>
         </is>
       </c>
     </row>
